--- a/research/traditional_assets/database/data/peru/peru_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/peru/peru_financial_svcs_non_bank_insurance.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0706</v>
+        <v>0.0308</v>
       </c>
       <c r="E2">
-        <v>-0.07969999999999999</v>
+        <v>-0.0607</v>
       </c>
       <c r="G2">
-        <v>0.3824742268041237</v>
+        <v>0.3472361809045226</v>
       </c>
       <c r="H2">
-        <v>0.3824742268041237</v>
+        <v>0.3472361809045226</v>
       </c>
       <c r="I2">
-        <v>0.2907216494845361</v>
+        <v>0.2065326633165829</v>
       </c>
       <c r="J2">
-        <v>0.2042792655401696</v>
+        <v>0.1496515363703765</v>
       </c>
       <c r="K2">
-        <v>4.69</v>
+        <v>4.11</v>
       </c>
       <c r="L2">
-        <v>0.2417525773195877</v>
+        <v>0.2065326633165829</v>
       </c>
       <c r="M2">
-        <v>4.31</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="N2">
-        <v>0.03489878542510121</v>
+        <v>0.08431550317316411</v>
       </c>
       <c r="O2">
-        <v>0.9189765458422173</v>
+        <v>2.262773722627737</v>
       </c>
       <c r="P2">
-        <v>4.31</v>
+        <v>4.27</v>
       </c>
       <c r="Q2">
-        <v>0.03489878542510121</v>
+        <v>0.03871260199456029</v>
       </c>
       <c r="R2">
-        <v>0.9189765458422173</v>
+        <v>1.038929440389294</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>5.030000000000001</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.5408602150537635</v>
       </c>
       <c r="U2">
-        <v>2.94</v>
+        <v>5.08</v>
       </c>
       <c r="V2">
-        <v>0.02380566801619433</v>
+        <v>0.04605621033544878</v>
       </c>
       <c r="W2">
-        <v>0.08375</v>
+        <v>0.08370672097759675</v>
       </c>
       <c r="X2">
-        <v>0.02640744929902174</v>
+        <v>0.05294960955937955</v>
       </c>
       <c r="Y2">
-        <v>0.05734255070097827</v>
+        <v>0.0307571114182172</v>
       </c>
       <c r="Z2">
-        <v>0.4946455889852116</v>
+        <v>0.5844346549192363</v>
       </c>
       <c r="AA2">
-        <v>0.1010458376205836</v>
+        <v>0.08746154401675453</v>
       </c>
       <c r="AB2">
-        <v>0.02639034416209034</v>
+        <v>0.05268493170072122</v>
       </c>
       <c r="AC2">
-        <v>0.07465549345849329</v>
+        <v>0.03477661231603331</v>
       </c>
       <c r="AD2">
-        <v>5.99</v>
+        <v>5.26</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5.99</v>
+        <v>5.26</v>
       </c>
       <c r="AG2">
-        <v>3.05</v>
+        <v>0.1799999999999997</v>
       </c>
       <c r="AH2">
-        <v>0.04625839833191752</v>
+        <v>0.04551748009691935</v>
       </c>
       <c r="AI2">
-        <v>0.1073669116329091</v>
+        <v>0.1018195896244677</v>
       </c>
       <c r="AJ2">
-        <v>0.02410114579217701</v>
+        <v>0.001629254163649527</v>
       </c>
       <c r="AK2">
-        <v>0.0577105014191107</v>
+        <v>0.003864319450407894</v>
       </c>
       <c r="AL2">
-        <v>0.198</v>
+        <v>0.426</v>
       </c>
       <c r="AM2">
-        <v>0.198</v>
+        <v>-0.804</v>
       </c>
       <c r="AN2">
-        <v>1.041739130434783</v>
+        <v>1.093555093555094</v>
       </c>
       <c r="AO2">
-        <v>28.48484848484848</v>
+        <v>9.647887323943664</v>
       </c>
       <c r="AP2">
-        <v>0.5304347826086957</v>
+        <v>0.03742203742203737</v>
       </c>
       <c r="AQ2">
-        <v>28.48484848484848</v>
+        <v>-5.111940298507463</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0706</v>
+        <v>0.0308</v>
       </c>
       <c r="E3">
-        <v>-0.07969999999999999</v>
+        <v>-0.0607</v>
       </c>
       <c r="G3">
-        <v>0.3824742268041237</v>
+        <v>0.3472361809045226</v>
       </c>
       <c r="H3">
-        <v>0.3824742268041237</v>
+        <v>0.3472361809045226</v>
       </c>
       <c r="I3">
-        <v>0.2907216494845361</v>
+        <v>0.2065326633165829</v>
       </c>
       <c r="J3">
-        <v>0.2042792655401696</v>
+        <v>0.1496515363703765</v>
       </c>
       <c r="K3">
-        <v>4.69</v>
+        <v>4.11</v>
       </c>
       <c r="L3">
-        <v>0.2417525773195877</v>
+        <v>0.2065326633165829</v>
       </c>
       <c r="M3">
-        <v>4.31</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="N3">
-        <v>0.03489878542510121</v>
+        <v>0.08431550317316411</v>
       </c>
       <c r="O3">
-        <v>0.9189765458422173</v>
+        <v>2.262773722627737</v>
       </c>
       <c r="P3">
-        <v>4.31</v>
+        <v>4.27</v>
       </c>
       <c r="Q3">
-        <v>0.03489878542510121</v>
+        <v>0.03871260199456029</v>
       </c>
       <c r="R3">
-        <v>0.9189765458422173</v>
+        <v>1.038929440389294</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>5.030000000000001</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.5408602150537635</v>
       </c>
       <c r="U3">
-        <v>2.94</v>
+        <v>5.08</v>
       </c>
       <c r="V3">
-        <v>0.02380566801619433</v>
+        <v>0.04605621033544878</v>
       </c>
       <c r="W3">
-        <v>0.08375</v>
+        <v>0.08370672097759675</v>
       </c>
       <c r="X3">
-        <v>0.02640744929902174</v>
+        <v>0.05294960955937955</v>
       </c>
       <c r="Y3">
-        <v>0.05734255070097827</v>
+        <v>0.0307571114182172</v>
       </c>
       <c r="Z3">
-        <v>0.4946455889852116</v>
+        <v>0.5844346549192363</v>
       </c>
       <c r="AA3">
-        <v>0.1010458376205836</v>
+        <v>0.08746154401675453</v>
       </c>
       <c r="AB3">
-        <v>0.02639034416209034</v>
+        <v>0.05268493170072122</v>
       </c>
       <c r="AC3">
-        <v>0.07465549345849329</v>
+        <v>0.03477661231603331</v>
       </c>
       <c r="AD3">
-        <v>5.99</v>
+        <v>5.26</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5.99</v>
+        <v>5.26</v>
       </c>
       <c r="AG3">
-        <v>3.05</v>
+        <v>0.1799999999999997</v>
       </c>
       <c r="AH3">
-        <v>0.04625839833191752</v>
+        <v>0.04551748009691935</v>
       </c>
       <c r="AI3">
-        <v>0.1073669116329091</v>
+        <v>0.1018195896244677</v>
       </c>
       <c r="AJ3">
-        <v>0.02410114579217701</v>
+        <v>0.001629254163649527</v>
       </c>
       <c r="AK3">
-        <v>0.0577105014191107</v>
+        <v>0.003864319450407894</v>
       </c>
       <c r="AL3">
-        <v>0.198</v>
+        <v>0.426</v>
       </c>
       <c r="AM3">
-        <v>0.198</v>
+        <v>-0.804</v>
       </c>
       <c r="AN3">
-        <v>1.041739130434783</v>
+        <v>1.093555093555094</v>
       </c>
       <c r="AO3">
-        <v>28.48484848484848</v>
+        <v>9.647887323943664</v>
       </c>
       <c r="AP3">
-        <v>0.5304347826086957</v>
+        <v>0.03742203742203737</v>
       </c>
       <c r="AQ3">
-        <v>28.48484848484848</v>
+        <v>-5.111940298507463</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/peru/peru_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/peru/peru_financial_svcs_non_bank_insurance.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0308</v>
+        <v>0.05139999999999999</v>
       </c>
       <c r="E2">
-        <v>-0.0607</v>
+        <v>0.0471</v>
       </c>
       <c r="G2">
-        <v>0.3472361809045226</v>
+        <v>0.2950381679389313</v>
       </c>
       <c r="H2">
-        <v>0.3472361809045226</v>
+        <v>0.2950381679389313</v>
       </c>
       <c r="I2">
-        <v>0.2065326633165829</v>
+        <v>0.2717557251908397</v>
       </c>
       <c r="J2">
-        <v>0.1496515363703765</v>
+        <v>0.2010055277704659</v>
       </c>
       <c r="K2">
-        <v>4.11</v>
+        <v>8.51</v>
       </c>
       <c r="L2">
-        <v>0.2065326633165829</v>
+        <v>0.3248091603053435</v>
       </c>
       <c r="M2">
-        <v>9.300000000000001</v>
+        <v>10.66</v>
       </c>
       <c r="N2">
-        <v>0.08431550317316411</v>
+        <v>0.1077856420626896</v>
       </c>
       <c r="O2">
-        <v>2.262773722627737</v>
+        <v>1.252643948296122</v>
       </c>
       <c r="P2">
-        <v>4.27</v>
+        <v>5.37</v>
       </c>
       <c r="Q2">
-        <v>0.03871260199456029</v>
+        <v>0.05429726996966633</v>
       </c>
       <c r="R2">
-        <v>1.038929440389294</v>
+        <v>0.6310223266745006</v>
       </c>
       <c r="S2">
-        <v>5.030000000000001</v>
+        <v>5.29</v>
       </c>
       <c r="T2">
-        <v>0.5408602150537635</v>
+        <v>0.4962476547842402</v>
       </c>
       <c r="U2">
-        <v>5.08</v>
+        <v>4</v>
       </c>
       <c r="V2">
-        <v>0.04605621033544878</v>
+        <v>0.04044489383215369</v>
       </c>
       <c r="W2">
-        <v>0.08370672097759675</v>
+        <v>0.1858078602620087</v>
       </c>
       <c r="X2">
-        <v>0.05294960955937955</v>
+        <v>0.05598701137077978</v>
       </c>
       <c r="Y2">
-        <v>0.0307571114182172</v>
+        <v>0.129820848891229</v>
       </c>
       <c r="Z2">
-        <v>0.5844346549192363</v>
+        <v>0.9604105571847508</v>
       </c>
       <c r="AA2">
-        <v>0.08746154401675453</v>
+        <v>0.1930478309232481</v>
       </c>
       <c r="AB2">
-        <v>0.05268493170072122</v>
+        <v>0.055431457896011</v>
       </c>
       <c r="AC2">
-        <v>0.03477661231603331</v>
+        <v>0.1376163730272371</v>
       </c>
       <c r="AD2">
-        <v>5.26</v>
+        <v>4.82</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5.26</v>
+        <v>4.82</v>
       </c>
       <c r="AG2">
-        <v>0.1799999999999997</v>
+        <v>0.8200000000000003</v>
       </c>
       <c r="AH2">
-        <v>0.04551748009691935</v>
+        <v>0.04647126880061705</v>
       </c>
       <c r="AI2">
-        <v>0.1018195896244677</v>
+        <v>0.09832721338229294</v>
       </c>
       <c r="AJ2">
-        <v>0.001629254163649527</v>
+        <v>0.008223024468511836</v>
       </c>
       <c r="AK2">
-        <v>0.003864319450407894</v>
+        <v>0.01821412705464239</v>
       </c>
       <c r="AL2">
-        <v>0.426</v>
+        <v>0.327</v>
       </c>
       <c r="AM2">
-        <v>-0.804</v>
+        <v>-3.003</v>
       </c>
       <c r="AN2">
-        <v>1.093555093555094</v>
+        <v>0.5751789976133651</v>
       </c>
       <c r="AO2">
-        <v>9.647887323943664</v>
+        <v>21.7737003058104</v>
       </c>
       <c r="AP2">
-        <v>0.03742203742203737</v>
+        <v>0.09785202863961816</v>
       </c>
       <c r="AQ2">
-        <v>-5.111940298507463</v>
+        <v>-2.370962370962371</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0308</v>
+        <v>0.05139999999999999</v>
       </c>
       <c r="E3">
-        <v>-0.0607</v>
+        <v>0.0471</v>
       </c>
       <c r="G3">
-        <v>0.3472361809045226</v>
+        <v>0.2950381679389313</v>
       </c>
       <c r="H3">
-        <v>0.3472361809045226</v>
+        <v>0.2950381679389313</v>
       </c>
       <c r="I3">
-        <v>0.2065326633165829</v>
+        <v>0.2717557251908397</v>
       </c>
       <c r="J3">
-        <v>0.1496515363703765</v>
+        <v>0.2010055277704659</v>
       </c>
       <c r="K3">
-        <v>4.11</v>
+        <v>8.51</v>
       </c>
       <c r="L3">
-        <v>0.2065326633165829</v>
+        <v>0.3248091603053435</v>
       </c>
       <c r="M3">
-        <v>9.300000000000001</v>
+        <v>10.66</v>
       </c>
       <c r="N3">
-        <v>0.08431550317316411</v>
+        <v>0.1077856420626896</v>
       </c>
       <c r="O3">
-        <v>2.262773722627737</v>
+        <v>1.252643948296122</v>
       </c>
       <c r="P3">
-        <v>4.27</v>
+        <v>5.37</v>
       </c>
       <c r="Q3">
-        <v>0.03871260199456029</v>
+        <v>0.05429726996966633</v>
       </c>
       <c r="R3">
-        <v>1.038929440389294</v>
+        <v>0.6310223266745006</v>
       </c>
       <c r="S3">
-        <v>5.030000000000001</v>
+        <v>5.29</v>
       </c>
       <c r="T3">
-        <v>0.5408602150537635</v>
+        <v>0.4962476547842402</v>
       </c>
       <c r="U3">
-        <v>5.08</v>
+        <v>4</v>
       </c>
       <c r="V3">
-        <v>0.04605621033544878</v>
+        <v>0.04044489383215369</v>
       </c>
       <c r="W3">
-        <v>0.08370672097759675</v>
+        <v>0.1858078602620087</v>
       </c>
       <c r="X3">
-        <v>0.05294960955937955</v>
+        <v>0.05598701137077978</v>
       </c>
       <c r="Y3">
-        <v>0.0307571114182172</v>
+        <v>0.129820848891229</v>
       </c>
       <c r="Z3">
-        <v>0.5844346549192363</v>
+        <v>0.9604105571847508</v>
       </c>
       <c r="AA3">
-        <v>0.08746154401675453</v>
+        <v>0.1930478309232481</v>
       </c>
       <c r="AB3">
-        <v>0.05268493170072122</v>
+        <v>0.055431457896011</v>
       </c>
       <c r="AC3">
-        <v>0.03477661231603331</v>
+        <v>0.1376163730272371</v>
       </c>
       <c r="AD3">
-        <v>5.26</v>
+        <v>4.82</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5.26</v>
+        <v>4.82</v>
       </c>
       <c r="AG3">
-        <v>0.1799999999999997</v>
+        <v>0.8200000000000003</v>
       </c>
       <c r="AH3">
-        <v>0.04551748009691935</v>
+        <v>0.04647126880061705</v>
       </c>
       <c r="AI3">
-        <v>0.1018195896244677</v>
+        <v>0.09832721338229294</v>
       </c>
       <c r="AJ3">
-        <v>0.001629254163649527</v>
+        <v>0.008223024468511836</v>
       </c>
       <c r="AK3">
-        <v>0.003864319450407894</v>
+        <v>0.01821412705464239</v>
       </c>
       <c r="AL3">
-        <v>0.426</v>
+        <v>0.327</v>
       </c>
       <c r="AM3">
-        <v>-0.804</v>
+        <v>-3.003</v>
       </c>
       <c r="AN3">
-        <v>1.093555093555094</v>
+        <v>0.5751789976133651</v>
       </c>
       <c r="AO3">
-        <v>9.647887323943664</v>
+        <v>21.7737003058104</v>
       </c>
       <c r="AP3">
-        <v>0.03742203742203737</v>
+        <v>0.09785202863961816</v>
       </c>
       <c r="AQ3">
-        <v>-5.111940298507463</v>
+        <v>-2.370962370962371</v>
       </c>
     </row>
   </sheetData>
